--- a/corr_matrix/residual_exam2C_3PL.xlsx
+++ b/corr_matrix/residual_exam2C_3PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2C01</t>
@@ -520,49 +525,49 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01400927142778818</v>
+        <v>-0.01402021516757527</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0364412582624734</v>
+        <v>0.03652105950488899</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1233600797851056</v>
+        <v>0.1235170671766554</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3064399678403969</v>
+        <v>-0.3061575117011249</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009905732150611855</v>
+        <v>0.01034573074178144</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2287195973309631</v>
+        <v>-0.2283950551373558</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0343547956508194</v>
+        <v>0.03445824185712082</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1810289718827228</v>
+        <v>-0.1806410920225622</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1372551182796635</v>
+        <v>-0.1368121027593821</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.08249482427720901</v>
+        <v>-0.08219840709828895</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1778995575508923</v>
+        <v>-0.1777200769652719</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.09885419269150113</v>
+        <v>-0.09879087433152946</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.01595436424366179</v>
+        <v>-0.01569909654493125</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3210768560207837</v>
+        <v>-0.3207338802789623</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.01392228376200789</v>
+        <v>-0.01367868284490066</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +577,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.01400927142778818</v>
+        <v>-0.01402021516757527</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1770661385629947</v>
+        <v>-0.1772859268533393</v>
       </c>
       <c r="E3" t="n">
-        <v>0.093514548529016</v>
+        <v>0.09347984824204518</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.09860458423969534</v>
+        <v>-0.09895493675477553</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.09957167282076547</v>
+        <v>-0.09952710399299526</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05478722609312457</v>
+        <v>0.054430559853687</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2576332688367865</v>
+        <v>0.2575535970169376</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2085994181421786</v>
+        <v>-0.2085716786853287</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1513355620023442</v>
+        <v>-0.151255012426498</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1598751423914221</v>
+        <v>-0.159845778967159</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1125969522641828</v>
+        <v>-0.1126687325892425</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.123682334107649</v>
+        <v>-0.1238453105873713</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2933463685952905</v>
+        <v>-0.2933184312388753</v>
       </c>
       <c r="P3" t="n">
-        <v>0.09332445098399986</v>
+        <v>0.09294437947878234</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1760302278936892</v>
+        <v>-0.176389853731102</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +632,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0364412582624734</v>
+        <v>0.03652105950488899</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1770661385629947</v>
+        <v>-0.1772859268533393</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1795789423332724</v>
+        <v>-0.1797133955662163</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01185192879993082</v>
+        <v>-0.01211437766559459</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01953067169267144</v>
+        <v>0.01958790877606643</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1220490616492035</v>
+        <v>-0.1224052462234065</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1408693707325692</v>
+        <v>-0.1409870773779967</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03311473310771914</v>
+        <v>0.03307958393798755</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.175888090889144</v>
+        <v>-0.1760068471450197</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1673146021583835</v>
+        <v>-0.1674290838496052</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009954394215639151</v>
+        <v>0.009870085557437932</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03771372407236714</v>
+        <v>0.03756837503398924</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09922778434524419</v>
+        <v>0.09901546545092181</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0682332704793563</v>
+        <v>-0.06856957448058748</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.07847203007155035</v>
+        <v>-0.07874460999905841</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +687,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1233600797851056</v>
+        <v>0.1235170671766554</v>
       </c>
       <c r="C5" t="n">
-        <v>0.093514548529016</v>
+        <v>0.09347984824204518</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1795789423332724</v>
+        <v>-0.1797133955662163</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02324925738965872</v>
+        <v>-0.02332069496218854</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.05544916540254492</v>
+        <v>-0.05526772123835522</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.04442258776924723</v>
+        <v>-0.04455892952910169</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2209784091274787</v>
+        <v>-0.2209310228284463</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1566738397048171</v>
+        <v>-0.1565699073619093</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.04764403367113455</v>
+        <v>-0.0473799713700327</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.03525540443443856</v>
+        <v>-0.03511176148048426</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2257628507169802</v>
+        <v>-0.2256760692395658</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2093162653704196</v>
+        <v>-0.2093077038021438</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.008018489663007305</v>
+        <v>-0.007881939060162444</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0984663909458315</v>
+        <v>0.09833863625384875</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02083453012195018</v>
+        <v>0.02078129976852925</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +742,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.3064399678403969</v>
+        <v>-0.3061575117011249</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.09860458423969534</v>
+        <v>-0.09895493675477553</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01185192879993082</v>
+        <v>-0.01211437766559459</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02324925738965872</v>
+        <v>-0.02332069496218854</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.06000040677498001</v>
+        <v>-0.05982651162771554</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.01510768201612272</v>
+        <v>-0.01564006404496881</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1927977596160156</v>
+        <v>-0.1929517606420013</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.03529660389499108</v>
+        <v>-0.03514607592369001</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.02938136942395176</v>
+        <v>-0.0293601575718894</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.07491233260664582</v>
+        <v>-0.07488204424647321</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.06750634858908375</v>
+        <v>-0.06761309913257824</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.06784922472738802</v>
+        <v>-0.06807440982234772</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01876330850932419</v>
+        <v>0.01863228193000068</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0991183282320468</v>
+        <v>0.09863649730361682</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.08737918059634989</v>
+        <v>-0.08786355894390367</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +797,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009905732150611855</v>
+        <v>0.01034573074178144</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.09957167282076547</v>
+        <v>-0.09952710399299526</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01953067169267144</v>
+        <v>0.01958790877606643</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.05544916540254492</v>
+        <v>-0.05526772123835522</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.06000040677498001</v>
+        <v>-0.05982651162771554</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4023973556272127</v>
+        <v>-0.4022761035060195</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1249607191375862</v>
+        <v>-0.1248501517208716</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.07554399267355787</v>
+        <v>-0.07528340979025032</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.05537189248857484</v>
+        <v>-0.05499978039069807</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.08397249982480694</v>
+        <v>-0.08372943429157444</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.04129066552418342</v>
+        <v>-0.04118055861142651</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.04191904558388557</v>
+        <v>-0.0418869857892374</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07468685592005003</v>
+        <v>0.07497314952891801</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1133983439581656</v>
+        <v>-0.1132697282773279</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1970107986646532</v>
+        <v>-0.1968256373365854</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +852,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.2287195973309631</v>
+        <v>-0.2283950551373558</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05478722609312457</v>
+        <v>0.054430559853687</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1220490616492035</v>
+        <v>-0.1224052462234065</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.04442258776924723</v>
+        <v>-0.04455892952910169</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01510768201612272</v>
+        <v>-0.01564006404496881</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4023973556272127</v>
+        <v>-0.4022761035060195</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1405654232622393</v>
+        <v>0.1405247871467738</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2093217038791281</v>
+        <v>-0.2092180036634289</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1092478062790165</v>
+        <v>0.1093537467176995</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1987496112954243</v>
+        <v>-0.1988246890036051</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1199260119965845</v>
+        <v>-0.1201255388437026</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0702613417303886</v>
+        <v>0.07003230919179575</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2558733348408379</v>
+        <v>-0.2560181664214543</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.03033203877580166</v>
+        <v>-0.03105599155294526</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2758601520046853</v>
+        <v>0.2754377371338353</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +907,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0343547956508194</v>
+        <v>0.03445824185712082</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2576332688367865</v>
+        <v>0.2575535970169376</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1408693707325692</v>
+        <v>-0.1409870773779967</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2209784091274787</v>
+        <v>-0.2209310228284463</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1927977596160156</v>
+        <v>-0.1929517606420013</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1249607191375862</v>
+        <v>-0.1248501517208716</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1405654232622393</v>
+        <v>0.1405247871467738</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.201892769639787</v>
+        <v>-0.2018162113765385</v>
       </c>
       <c r="K9" t="n">
-        <v>0.151841516122023</v>
+        <v>0.1519060712419522</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1189341790929729</v>
+        <v>-0.1188459123561266</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.04085397035074026</v>
+        <v>-0.04085554953824372</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.252702719320665</v>
+        <v>-0.2527928267682142</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1296604101412443</v>
+        <v>-0.1296205438362077</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1538991564961074</v>
+        <v>-0.154061310750898</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.008468778133531262</v>
+        <v>-0.008564073521356129</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +962,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1810289718827228</v>
+        <v>-0.1806410920225622</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2085994181421786</v>
+        <v>-0.2085716786853287</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03311473310771914</v>
+        <v>0.03307958393798755</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1566738397048171</v>
+        <v>-0.1565699073619093</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.03529660389499108</v>
+        <v>-0.03514607592369001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.07554399267355787</v>
+        <v>-0.07528340979025032</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2093217038791281</v>
+        <v>-0.2092180036634289</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.201892769639787</v>
+        <v>-0.2018162113765385</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1810262072316573</v>
+        <v>0.1810190641890394</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1082836371625091</v>
+        <v>0.1083794491622625</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1057405606764937</v>
+        <v>0.1058054104859462</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.06742142371606291</v>
+        <v>-0.06739257380959564</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.06994704959829749</v>
+        <v>-0.06997863288758485</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.09876639595473662</v>
+        <v>-0.09865994188817472</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1807121271444166</v>
+        <v>-0.1805732066328236</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1017,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1372551182796635</v>
+        <v>-0.1368121027593821</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1513355620023442</v>
+        <v>-0.151255012426498</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.175888090889144</v>
+        <v>-0.1760068471450197</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.04764403367113455</v>
+        <v>-0.0473799713700327</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.02938136942395176</v>
+        <v>-0.0293601575718894</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.05537189248857484</v>
+        <v>-0.05499978039069807</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1092478062790165</v>
+        <v>0.1093537467176995</v>
       </c>
       <c r="I11" t="n">
-        <v>0.151841516122023</v>
+        <v>0.1519060712419522</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1810262072316573</v>
+        <v>0.1810190641890394</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.04688479424444957</v>
+        <v>-0.04663090325738368</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.05265500994545997</v>
+        <v>-0.05248710601575964</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01299947399416063</v>
+        <v>0.01303665406506069</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1542543395376752</v>
+        <v>-0.1539678633982228</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2240722385594051</v>
+        <v>-0.2241111875888451</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.02176800872929794</v>
+        <v>0.02187450012198215</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1072,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.08249482427720901</v>
+        <v>-0.08219840709828895</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1598751423914221</v>
+        <v>-0.159845778967159</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1673146021583835</v>
+        <v>-0.1674290838496052</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.03525540443443856</v>
+        <v>-0.03511176148048426</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.07491233260664582</v>
+        <v>-0.07488204424647321</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.08397249982480694</v>
+        <v>-0.08372943429157444</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1987496112954243</v>
+        <v>-0.1988246890036051</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1189341790929729</v>
+        <v>-0.1188459123561266</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1082836371625091</v>
+        <v>0.1083794491622625</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.04688479424444957</v>
+        <v>-0.04663090325738368</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1039261716475059</v>
+        <v>-0.103836087477806</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1496405931165588</v>
+        <v>0.1496696457385126</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3428649823098631</v>
+        <v>0.3429644840095081</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.07035616519057429</v>
+        <v>-0.07042246053410943</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2272990323528425</v>
+        <v>-0.2272835370959067</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1127,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1778995575508923</v>
+        <v>-0.1777200769652719</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1125969522641828</v>
+        <v>-0.1126687325892425</v>
       </c>
       <c r="D13" t="n">
-        <v>0.009954394215639151</v>
+        <v>0.009870085557437932</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2257628507169802</v>
+        <v>-0.2256760692395658</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.06750634858908375</v>
+        <v>-0.06761309913257824</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.04129066552418342</v>
+        <v>-0.04118055861142651</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1199260119965845</v>
+        <v>-0.1201255388437026</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.04085397035074026</v>
+        <v>-0.04085554953824372</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1057405606764937</v>
+        <v>0.1058054104859462</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.05265500994545997</v>
+        <v>-0.05248710601575964</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1039261716475059</v>
+        <v>-0.103836087477806</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02369233110762317</v>
+        <v>0.02366339682426192</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1474686983904593</v>
+        <v>0.1475582600695197</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.08218353313193073</v>
+        <v>-0.08237880337860756</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.03675885312604589</v>
+        <v>-0.0368596243994536</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1182,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.09885419269150113</v>
+        <v>-0.09879087433152946</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.123682334107649</v>
+        <v>-0.1238453105873713</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03771372407236714</v>
+        <v>0.03756837503398924</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2093162653704196</v>
+        <v>-0.2093077038021438</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.06784922472738802</v>
+        <v>-0.06807440982234772</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.04191904558388557</v>
+        <v>-0.0418869857892374</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0702613417303886</v>
+        <v>0.07003230919179575</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.252702719320665</v>
+        <v>-0.2527928267682142</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.06742142371606291</v>
+        <v>-0.06739257380959564</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01299947399416063</v>
+        <v>0.01303665406506069</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1496405931165588</v>
+        <v>0.1496696457385126</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02369233110762317</v>
+        <v>0.02366339682426192</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.05209333918659115</v>
+        <v>0.05205552868370771</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.07808244274367049</v>
+        <v>-0.07837373669242284</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.135739724889508</v>
+        <v>-0.1359838748237556</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1237,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.01595436424366179</v>
+        <v>-0.01569909654493125</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.2933463685952905</v>
+        <v>-0.2933184312388753</v>
       </c>
       <c r="D15" t="n">
-        <v>0.09922778434524419</v>
+        <v>0.09901546545092181</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.008018489663007305</v>
+        <v>-0.007881939060162444</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01876330850932419</v>
+        <v>0.01863228193000068</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07468685592005003</v>
+        <v>0.07497314952891801</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2558733348408379</v>
+        <v>-0.2560181664214543</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1296604101412443</v>
+        <v>-0.1296205438362077</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.06994704959829749</v>
+        <v>-0.06997863288758485</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1542543395376752</v>
+        <v>-0.1539678633982228</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3428649823098631</v>
+        <v>0.3429644840095081</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1474686983904593</v>
+        <v>0.1475582600695197</v>
       </c>
       <c r="N15" t="n">
-        <v>0.05209333918659115</v>
+        <v>0.05205552868370771</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.02883019321788181</v>
+        <v>-0.02902974046467247</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2242886472857984</v>
+        <v>-0.2243489151735837</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1292,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.3210768560207837</v>
+        <v>-0.3207338802789623</v>
       </c>
       <c r="C16" t="n">
-        <v>0.09332445098399986</v>
+        <v>0.09294437947878234</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0682332704793563</v>
+        <v>-0.06856957448058748</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0984663909458315</v>
+        <v>0.09833863625384875</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0991183282320468</v>
+        <v>0.09863649730361682</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1133983439581656</v>
+        <v>-0.1132697282773279</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.03033203877580166</v>
+        <v>-0.03105599155294526</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1538991564961074</v>
+        <v>-0.154061310750898</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.09876639595473662</v>
+        <v>-0.09865994188817472</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2240722385594051</v>
+        <v>-0.2241111875888451</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.07035616519057429</v>
+        <v>-0.07042246053410943</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.08218353313193073</v>
+        <v>-0.08237880337860756</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.07808244274367049</v>
+        <v>-0.07837373669242284</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.02883019321788181</v>
+        <v>-0.02902974046467247</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.06854131828964405</v>
+        <v>-0.06919389465880496</v>
       </c>
     </row>
     <row r="17">
@@ -1342,49 +1347,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.01392228376200789</v>
+        <v>-0.01367868284490066</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1760302278936892</v>
+        <v>-0.176389853731102</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.07847203007155035</v>
+        <v>-0.07874460999905841</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02083453012195018</v>
+        <v>0.02078129976852925</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.08737918059634989</v>
+        <v>-0.08786355894390367</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1970107986646532</v>
+        <v>-0.1968256373365854</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2758601520046853</v>
+        <v>0.2754377371338353</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.008468778133531262</v>
+        <v>-0.008564073521356129</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1807121271444166</v>
+        <v>-0.1805732066328236</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02176800872929794</v>
+        <v>0.02187450012198215</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2272990323528425</v>
+        <v>-0.2272835370959067</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.03675885312604589</v>
+        <v>-0.0368596243994536</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.135739724889508</v>
+        <v>-0.1359838748237556</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2242886472857984</v>
+        <v>-0.2243489151735837</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.06854131828964405</v>
+        <v>-0.06919389465880496</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
